--- a/src/data/SummitInfo.xlsx
+++ b/src/data/SummitInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbp-m1/Documents/AI Projects/my-home-info/src/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0E40B5A-B3E7-9147-B344-D10C5E43D3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24F05D7-CC06-6448-913F-930D0C402D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2080" yWindow="3880" windowWidth="28040" windowHeight="17180" xr2:uid="{529CB750-665A-8246-88D0-B89985134700}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Electric</t>
   </si>
@@ -108,6 +108,15 @@
   </si>
   <si>
     <t>https://mypec.com/</t>
+  </si>
+  <si>
+    <t>Texas Disposal Systems</t>
+  </si>
+  <si>
+    <t>512-263-5265</t>
+  </si>
+  <si>
+    <t>https://www.texasdisposal.com</t>
   </si>
 </sst>
 </file>
@@ -569,6 +578,15 @@
       <c r="B4" t="s">
         <v>9</v>
       </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
@@ -601,6 +619,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F5" r:id="rId1" display="tel:+1-(512)858-2390" xr:uid="{882E6151-8B67-DD4B-B848-62E0B26015C6}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=texas+disposal+systems&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{7325A5F9-04E6-6143-B470-05F00D57531B}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{94C789B0-6FB4-6C4D-BA68-D79D68B2207F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
